--- a/PC_2014/E__ScanF20_PC_028.xlsx
+++ b/PC_2014/E__ScanF20_PC_028.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +176,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,11 +560,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -522,117 +617,122 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Chennamaneni Vidya Sagar Rao</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Ponnam Prabhakar</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Burla Ravi</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Byagari Laxman</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Vinod Kumar Boinapally</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dr. Dharmaiah Vendavetla</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Lenkala Prabhakar Reddy</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Meesala Raji Reddy</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Ranaveni Lakshman</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Reddi Malla Srinivas</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Shaik Mohmood</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Uppuleti Laxman</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Kandem Prabhakar</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Pulikota Ramesh</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Mallesh Yadav Barla</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Mommed Amjad Mohiuddin</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Srinvas Reddy Lingampally</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -642,8 +742,10 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 2</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
@@ -652,72 +754,78 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>299</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>307</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="Q6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" s="4" t="n">
         <v>868</v>
       </c>
-      <c r="X6" s="4" t="n">
-        <v>845</v>
+      <c r="Y6" s="4">
+        <f>SUM(C6:S6)-T6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 3</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>0</v>
@@ -726,146 +834,158 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="Q7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>525</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>SUM(C7:S7)-T7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 4</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>53779</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>19814</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>408</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2038</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>48130</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>419</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>292</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>1066</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>4983</v>
       </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
         <v>705</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>1227</v>
       </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>478</v>
       </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" s="4" t="n">
         <v>136160</v>
       </c>
-      <c r="X8" s="4" t="n">
-        <v>133599</v>
+      <c r="Y8" s="4">
+        <f>SUM(C8:S8)-T8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 7</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>0</v>
@@ -892,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="N9" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>0</v>
@@ -910,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>0</v>
@@ -931,15 +1051,21 @@
         <v>0</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <f>SUM(C9:S9)-T9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 8</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>0</v>
@@ -993,149 +1119,161 @@
         <v>0</v>
       </c>
       <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="X10" s="4" t="n">
-        <v>0</v>
+      <c r="Y10" s="4">
+        <f>SUM(C10:S10)-T10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 9</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>351</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>879</v>
       </c>
-      <c r="V11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4" t="n">
         <v>879</v>
       </c>
-      <c r="X11" s="4" t="n">
-        <v>856</v>
+      <c r="Y11" s="4">
+        <f>SUM(C11:S11)-T11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 10</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>0</v>
@@ -1150,22 +1288,28 @@
         <v>0</v>
       </c>
       <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4" t="n">
         <v>683</v>
       </c>
-      <c r="X12" s="4" t="n">
-        <v>524</v>
+      <c r="Y12" s="4">
+        <f>SUM(C12:S12)-T12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 11</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="4" t="n">
         <v>0</v>
       </c>
@@ -1173,20 +1317,20 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
@@ -1194,176 +1338,188 @@
         <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>2</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="V13" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="W13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="4" t="n">
         <v>735</v>
       </c>
-      <c r="X13" s="4" t="n">
-        <v>316</v>
+      <c r="Y13" s="4">
+        <f>SUM(C13:S13)-T13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 14</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>259</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="L14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S14" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="T14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4" t="n">
         <v>590</v>
       </c>
-      <c r="V14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4" t="n">
         <v>590</v>
       </c>
-      <c r="X14" s="4" t="n">
-        <v>581</v>
+      <c r="Y14" s="4">
+        <f>SUM(C14:S14)-T14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 98</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S15" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="T15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
@@ -1375,34 +1531,40 @@
         <v>0</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>106</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <f>SUM(C15:S15)-T15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 102</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="H16" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I16" s="4" t="n">
         <v>2</v>
       </c>
@@ -1413,164 +1575,176 @@
         <v>2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="U16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="V16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="n">
         <v>561</v>
       </c>
-      <c r="X16" s="4" t="n">
-        <v>236</v>
+      <c r="Y16" s="4">
+        <f>SUM(C16:S16)-T16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 104</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>364</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>261</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="I17" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="S17" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="T17" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4" t="n">
         <v>735</v>
       </c>
-      <c r="V17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="X17" s="4" t="n">
-        <v>727</v>
+      <c r="Y17" s="4">
+        <f>SUM(C17:S17)-T17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 113</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="D18" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="I18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>1</v>
@@ -1579,146 +1753,158 @@
         <v>1</v>
       </c>
       <c r="R18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="S18" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="T18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="4" t="n">
         <v>298</v>
       </c>
-      <c r="V18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4" t="n">
         <v>298</v>
       </c>
-      <c r="X18" s="4" t="n">
-        <v>302</v>
+      <c r="Y18" s="4">
+        <f>SUM(C18:S18)-T18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>0</v>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 116</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>356</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="F19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="S19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="T19" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="U19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="X19" s="4" t="n">
-        <v>781</v>
+      <c r="Y19" s="4">
+        <f>SUM(C19:S19)-T19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 121</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="E20" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="4" t="n">
         <v>334</v>
       </c>
-      <c r="H20" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="I20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="K20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="M20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="N20" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>4</v>
@@ -1730,111 +1916,123 @@
         <v>4</v>
       </c>
       <c r="S20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T20" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="U20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="4" t="n">
         <v>928</v>
       </c>
-      <c r="V20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="4" t="n">
         <v>928</v>
       </c>
-      <c r="X20" s="4" t="n">
-        <v>875</v>
+      <c r="Y20" s="4">
+        <f>SUM(C20:S20)-T20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 122</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>184</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F21" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="N21" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4" t="n">
         <v>469</v>
       </c>
-      <c r="V21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="4" t="n">
         <v>469</v>
       </c>
-      <c r="X21" s="4" t="n">
-        <v>433</v>
+      <c r="Y21" s="4">
+        <f>SUM(C21:S21)-T21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 130</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" s="4" t="n">
         <v>0</v>
       </c>
@@ -1842,11 +2040,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
       </c>
@@ -1854,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
@@ -1869,120 +2067,132 @@
         <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="S22" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="T22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="4" t="n">
         <v>609</v>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="W22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="W22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="X22" s="4" t="n">
-        <v>487</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4">
+        <f>SUM(C22:S22)-T22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 131</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <v>265</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="T23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="V23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>305</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4">
+        <f>SUM(C23:S23)-T23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 132</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>190</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1990,150 +2200,162 @@
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="n">
         <v>378</v>
       </c>
-      <c r="V24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="X24" s="4" t="n">
-        <v>339</v>
+      <c r="Y24" s="4">
+        <f>SUM(C24:S24)-T24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 136</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="F25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>263</v>
       </c>
-      <c r="H25" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I25" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P25" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="Q25" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>5</v>
       </c>
       <c r="U25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V25" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="V25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="X25" s="4" t="n">
-        <v>607</v>
+      <c r="Y25" s="4">
+        <f>SUM(C25:S25)-T25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 137</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>172</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
       </c>
@@ -2156,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="4" t="n">
         <v>0</v>
@@ -2189,15 +2411,21 @@
         <v>0</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>176</v>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <f>SUM(C26:S26)-T26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 138</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -2209,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>0</v>
@@ -2263,175 +2491,364 @@
         <v>0</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="4">
+        <f>SUM(C27:S27)-T27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 139</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="P28" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="P28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="X28" s="4" t="n">
-        <v>519</v>
+      <c r="Y28" s="4">
+        <f>SUM(C28:S28)-T28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B29" s="6">
-        <f>SUM(B6:B28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="6">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="C29" s="8">
         <f>SUM(C6:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="8">
         <f>SUM(D6:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="8">
         <f>SUM(E6:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="8">
         <f>SUM(F6:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="8">
         <f>SUM(G6:G28)</f>
         <v/>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="8">
         <f>SUM(H6:H28)</f>
         <v/>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="8">
         <f>SUM(I6:I28)</f>
         <v/>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="8">
         <f>SUM(J6:J28)</f>
         <v/>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="8">
         <f>SUM(K6:K28)</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="8">
         <f>SUM(L6:L28)</f>
         <v/>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="8">
         <f>SUM(M6:M28)</f>
         <v/>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="8">
         <f>SUM(N6:N28)</f>
         <v/>
       </c>
-      <c r="O29" s="6">
+      <c r="O29" s="8">
         <f>SUM(O6:O28)</f>
         <v/>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="8">
         <f>SUM(P6:P28)</f>
         <v/>
       </c>
-      <c r="Q29" s="6">
+      <c r="Q29" s="8">
         <f>SUM(Q6:Q28)</f>
         <v/>
       </c>
-      <c r="R29" s="6">
+      <c r="R29" s="8">
         <f>SUM(R6:R28)</f>
         <v/>
       </c>
-      <c r="S29" s="6">
+      <c r="S29" s="8">
         <f>SUM(S6:S28)</f>
         <v/>
       </c>
-      <c r="T29" s="6">
+      <c r="T29" s="8">
         <f>SUM(T6:T28)</f>
         <v/>
       </c>
-      <c r="U29" s="6">
+      <c r="U29" s="8">
         <f>SUM(U6:U28)</f>
         <v/>
       </c>
-      <c r="V29" s="6">
+      <c r="V29" s="8">
         <f>SUM(V6:V28)</f>
         <v/>
       </c>
-      <c r="W29" s="6">
-        <f>SUM(W6:W28)</f>
+      <c r="W29" s="8">
+        <f>T29+U29</f>
+        <v/>
+      </c>
+      <c r="X29" s="8">
+        <f>SUM(X6:X28)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="8">
+        <f>SUM(C29:S29)-T29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="C31" s="12">
+        <f>C29+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="12">
+        <f>D29+D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="12">
+        <f>F29+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>G29+G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="12">
+        <f>H29+H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="12">
+        <f>I29+I30</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>J29+J30</f>
+        <v/>
+      </c>
+      <c r="K31" s="12">
+        <f>K29+K30</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>L29+L30</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>M29+M30</f>
+        <v/>
+      </c>
+      <c r="N31" s="12">
+        <f>N29+N30</f>
+        <v/>
+      </c>
+      <c r="O31" s="12">
+        <f>O29+O30</f>
+        <v/>
+      </c>
+      <c r="P31" s="12">
+        <f>P29+P30</f>
+        <v/>
+      </c>
+      <c r="Q31" s="12">
+        <f>Q29+Q30</f>
+        <v/>
+      </c>
+      <c r="R31" s="12">
+        <f>R29+R30</f>
+        <v/>
+      </c>
+      <c r="S31" s="12">
+        <f>S29+S30</f>
+        <v/>
+      </c>
+      <c r="T31" s="12">
+        <f>T29+T30</f>
+        <v/>
+      </c>
+      <c r="U31" s="12">
+        <f>U29+U30</f>
+        <v/>
+      </c>
+      <c r="V31" s="12">
+        <f>V29+V30</f>
+        <v/>
+      </c>
+      <c r="W31" s="12">
+        <f>W29+W30</f>
+        <v/>
+      </c>
+      <c r="X31" s="12">
+        <f>X29+X30</f>
+        <v/>
+      </c>
+      <c r="Y31" s="12">
+        <f>SUM(C31:S31)-T31</f>
         <v/>
       </c>
     </row>

--- a/PC_2014/E__ScanF20_PC_028.xlsx
+++ b/PC_2014/E__ScanF20_PC_028.xlsx
@@ -1391,13 +1391,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="32" customWidth="1" style="1" min="1" max="2"/>
+    <col width="32" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" customWidth="1" style="1" min="2" max="2"/>
     <col width="31" customWidth="1" style="1" min="3" max="3"/>
     <col width="19" customWidth="1" style="1" min="4" max="4"/>
-    <col width="15" customWidth="1" style="1" min="5" max="5"/>
+    <col width="16" customWidth="1" style="1" min="5" max="5"/>
     <col width="17" customWidth="1" style="1" min="6" max="6"/>
     <col width="25" customWidth="1" style="1" min="7" max="7"/>
     <col width="27" customWidth="1" style="1" min="8" max="8"/>
@@ -1414,7 +1415,7 @@
     <col width="28" customWidth="1" style="1" min="19" max="19"/>
     <col width="20" customWidth="1" style="1" min="20" max="20"/>
     <col width="17" customWidth="1" style="1" min="21" max="21"/>
-    <col width="15" customWidth="1" style="1" min="22" max="23"/>
+    <col width="16" customWidth="1" style="1" min="22" max="23"/>
     <col width="17" customWidth="1" style="1" min="24" max="24"/>
     <col width="8.851559999999999" customWidth="1" style="1" min="25" max="16384"/>
   </cols>
@@ -1659,11 +1660,11 @@
     </row>
     <row r="6" ht="12.7" customHeight="1" s="22">
       <c r="A6" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 4</t>
+          <t>" iain</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
@@ -1697,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N6" s="11" t="n">
         <v>0</v>
@@ -1718,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U6" s="12" t="n">
         <v>0</v>
@@ -1727,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X6" s="12" t="n">
         <v>0</v>
@@ -1735,151 +1736,151 @@
     </row>
     <row r="7" ht="12.7" customHeight="1" s="22">
       <c r="A7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 5</t>
+          <t>ae</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T7" s="12" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="U7" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W7" s="12" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="X7" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="12.7" customHeight="1" s="22">
       <c r="A8" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 6</t>
+          <t>Porumalla</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="11" t="n">
         <v>4</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="12" t="n">
-        <v>432</v>
+        <v>560</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="12" t="n">
-        <v>442</v>
+        <v>569</v>
       </c>
       <c r="X8" s="12" t="n">
         <v>0</v>
@@ -1887,27 +1888,27 @@
     </row>
     <row r="9" ht="12.7" customHeight="1" s="22">
       <c r="A9" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 7</t>
+          <t>Medipalli</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>13</v>
+        <v>274</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>2</v>
@@ -1916,62 +1917,62 @@
         <v>2</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T9" s="12" t="n">
-        <v>127</v>
+        <v>528</v>
       </c>
       <c r="U9" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W9" s="12" t="n">
-        <v>143</v>
+        <v>528</v>
       </c>
       <c r="X9" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="12.7" customHeight="1" s="22">
       <c r="A10" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 8</t>
+          <t>Katlakunta</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>0</v>
@@ -1980,58 +1981,58 @@
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>259</v>
+        <v>6</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S10" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" s="12" t="n">
-        <v>569</v>
+        <v>337</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W10" s="12" t="n">
-        <v>576</v>
+        <v>337</v>
       </c>
       <c r="X10" s="12" t="n">
         <v>0</v>
@@ -2039,75 +2040,75 @@
     </row>
     <row r="11" ht="12.7" customHeight="1" s="22">
       <c r="A11" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 9</t>
+          <t>Rancaa puur</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" s="11" t="n">
         <v>3</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" s="12" t="n">
-        <v>659</v>
+        <v>55</v>
       </c>
       <c r="U11" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W11" s="12" t="n">
-        <v>669</v>
+        <v>55</v>
       </c>
       <c r="X11" s="12" t="n">
         <v>0</v>
@@ -2115,42 +2116,42 @@
     </row>
     <row r="12" ht="12.7" customHeight="1" s="22">
       <c r="A12" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 10</t>
+          <t>IGovindaram</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>330</v>
+        <v>1</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12" s="11" t="n">
         <v>0</v>
@@ -2162,68 +2163,68 @@
         <v>0</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S12" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T12" s="12" t="n">
-        <v>401</v>
+        <v>270</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W12" s="12" t="n">
-        <v>415</v>
+        <v>270</v>
       </c>
       <c r="X12" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="12.7" customHeight="1" s="22">
       <c r="A13" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 11</t>
+          <t>VER erro</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="11" t="n">
         <v>0</v>
@@ -2235,107 +2236,107 @@
         <v>0</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>24</v>
+        <v>278</v>
       </c>
       <c r="X13" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="12.7" customHeight="1" s="22">
       <c r="A14" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 12</t>
+          <t>Tombaraopet</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S14" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" s="12" t="n">
-        <v>67</v>
+        <v>537</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W14" s="12" t="n">
-        <v>69</v>
+        <v>537</v>
       </c>
       <c r="X14" s="12" t="n">
         <v>0</v>
@@ -2343,118 +2344,118 @@
     </row>
     <row r="15" ht="12.7" customHeight="1" s="22">
       <c r="A15" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 13</t>
+          <t>ee</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0</v>
+        <v>1192</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>1306</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="12" t="n">
-        <v>1816</v>
+        <v>1348</v>
       </c>
       <c r="U15" s="12" t="n">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="W15" s="12" t="n">
-        <v>2198</v>
+        <v>1351</v>
       </c>
       <c r="X15" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="12.7" customHeight="1" s="22">
       <c r="A16" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 14</t>
+          <t>ee)</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" s="11" t="n">
         <v>0</v>
@@ -2463,59 +2464,59 @@
         <v>0</v>
       </c>
       <c r="O16" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" s="11" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="12" t="n">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="U16" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="W16" s="12" t="n">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="X16" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="12.7" customHeight="1" s="22">
       <c r="A17" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 15</t>
+          <t>MEDIPALLI</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0</v>
@@ -2527,43 +2528,43 @@
         <v>0</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T17" s="12" t="n">
-        <v>10</v>
+        <v>1384</v>
       </c>
       <c r="U17" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W17" s="12" t="n">
-        <v>67</v>
+        <v>1384</v>
       </c>
       <c r="X17" s="12" t="n">
         <v>0</v>
@@ -2571,75 +2572,75 @@
     </row>
     <row r="18" ht="12.7" customHeight="1" s="22">
       <c r="A18" s="9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Polling Station 16</t>
+          <t>a -_</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" s="11" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="12" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="U18" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W18" s="12" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="X18" s="12" t="n">
         <v>0</v>
@@ -2647,18 +2648,18 @@
     </row>
     <row r="19" ht="12.7" customHeight="1" s="22">
       <c r="A19" s="9" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>tHAo.) a1 | 207 | 7 | 2 | us| o | o | o | «4 | 3 | a] of} 2 | 2]a] 2} wl es] ae | o | ms | O]</t>
+          <t>el</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>0</v>
@@ -2676,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>0</v>
@@ -2691,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="11" t="n">
         <v>0</v>
@@ -2706,16 +2707,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="12" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="U19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="X19" s="12" t="n">
         <v>0</v>
@@ -2723,300 +2724,8280 @@
     </row>
     <row r="20" ht="12.7" customHeight="1" s="22">
       <c r="A20" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Konda pur</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="U20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="12.7" customHeight="1" s="22">
+      <c r="A21" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Konda puur</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="U21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="X21" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="12.7" customHeight="1" s="22">
+      <c r="A22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Konda puur</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>1101</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" s="12" t="n">
+        <v>1168</v>
+      </c>
+      <c r="U22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="12" t="n">
+        <v>1168</v>
+      </c>
+      <c r="X22" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="12.7" customHeight="1" s="22">
+      <c r="A23" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Vilyathabad</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="U23" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="V23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="X23" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="12.7" customHeight="1" s="22">
+      <c r="A24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Vallampally</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>258</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" s="12" t="n">
+        <v>598</v>
+      </c>
+      <c r="U24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="12" t="n">
+        <v>598</v>
+      </c>
+      <c r="X24" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="12.7" customHeight="1" s="22">
+      <c r="A25" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Machaapuur</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>131</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="U25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="X25" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="12.7" customHeight="1" s="22">
+      <c r="A26" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>\Kalva kota</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>239</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" s="12" t="n">
+        <v>547</v>
+      </c>
+      <c r="U26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="12" t="n">
+        <v>547</v>
+      </c>
+      <c r="X26" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="12.7" customHeight="1" s="22">
+      <c r="A27" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Bheemaram |</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="X27" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="12.7" customHeight="1" s="22">
+      <c r="A28" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 44</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="U28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="X28" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="12.7" customHeight="1" s="22">
+      <c r="A29" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>;isiteaeea</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="U29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="X29" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="12.7" customHeight="1" s="22">
+      <c r="A30" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Sirikonda |</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="U30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="12" t="n">
+        <v>1188</v>
+      </c>
+      <c r="X30" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="12.7" customHeight="1" s="22">
+      <c r="A31" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Takkallapally</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>252</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>288</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="12" t="n">
+        <v>657</v>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="12" t="n">
+        <v>657</v>
+      </c>
+      <c r="X31" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="12.7" customHeight="1" s="22">
+      <c r="A32" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Takkallapally</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="U32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="X32" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="12.7" customHeight="1" s="22">
+      <c r="A33" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>'Takkalapalli</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>232</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="12" t="n">
+        <v>368</v>
+      </c>
+      <c r="U33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="12" t="n">
+        <v>368</v>
+      </c>
+      <c r="X33" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="12.7" customHeight="1" s="22">
+      <c r="A34" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>ergs</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="U34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="X34" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="12.7" customHeight="1" s="22">
+      <c r="A35" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>IOotpalli.</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>190</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>286</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="12" t="n">
+        <v>558</v>
+      </c>
+      <c r="U35" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="12" t="n">
+        <v>585</v>
+      </c>
+      <c r="X35" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" ht="12.7" customHeight="1" s="22">
+      <c r="A36" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>IRhuehanrag peta</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>1153</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="12" t="n">
+        <v>1380</v>
+      </c>
+      <c r="U36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="12" t="n">
+        <v>1380</v>
+      </c>
+      <c r="X36" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="12.7" customHeight="1" s="22">
+      <c r="A37" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>—————</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>307</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="12" t="n">
+        <v>309</v>
+      </c>
+      <c r="U37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="12" t="n">
+        <v>309</v>
+      </c>
+      <c r="X37" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="12.7" customHeight="1" s="22">
+      <c r="A38" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>IChinthakunta</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>299</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="12" t="n">
+        <v>369</v>
+      </c>
+      <c r="U38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="12" t="n">
+        <v>369</v>
+      </c>
+      <c r="X38" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="12.7" customHeight="1" s="22">
+      <c r="A39" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Ambaripeta</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>152</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="12" t="n">
+        <v>469</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="12" t="n">
+        <v>469</v>
+      </c>
+      <c r="X39" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="12.7" customHeight="1" s="22">
+      <c r="A40" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>AmbDaripeta |</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>322</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" s="12" t="n">
+        <v>395</v>
+      </c>
+      <c r="U40" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="X40" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="12.7" customHeight="1" s="22">
+      <c r="A41" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Rudrangi</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>428</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T41" s="12" t="n">
+        <v>624</v>
+      </c>
+      <c r="U41" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="12" t="n">
+        <v>626</v>
+      </c>
+      <c r="X41" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" ht="12.7" customHeight="1" s="22">
+      <c r="A42" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Nudrangi</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>436</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" s="12" t="n">
+        <v>618</v>
+      </c>
+      <c r="U42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="12" t="n">
+        <v>618</v>
+      </c>
+      <c r="X42" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="12.7" customHeight="1" s="22">
+      <c r="A43" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Rudrangi</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="U43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W43" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="X43" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="12.7" customHeight="1" s="22">
+      <c r="A44" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Rudrangi</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>507</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O44" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P44" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" s="12" t="n">
+        <v>572</v>
+      </c>
+      <c r="U44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="12" t="n">
+        <v>572</v>
+      </c>
+      <c r="X44" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="12.7" customHeight="1" s="22">
+      <c r="A45" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Rudrangi-</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S45" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="U45" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="12" t="n">
+        <v>249</v>
+      </c>
+      <c r="X45" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" ht="12.7" customHeight="1" s="22">
+      <c r="A46" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Malyala</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>387</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>222</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P46" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S46" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" s="12" t="n">
+        <v>711</v>
+      </c>
+      <c r="U46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="12" t="n">
+        <v>711</v>
+      </c>
+      <c r="X46" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" ht="12.7" customHeight="1" s="22">
+      <c r="A47" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="U47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="X47" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="12.7" customHeight="1" s="22">
+      <c r="A48" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>|Venkatravu peta | | 236 | 184 | ee ee ee ee ee ee ee ee ee ee ee ee Se ee ee ee ee ee ee ee ee be | 829 | O | 829</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="13.65" customHeight="1" s="22">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Venkatravu peta</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>283</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N48" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R48" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="12" t="n">
+        <v>357</v>
+      </c>
+      <c r="U48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="12" t="n">
+        <v>357</v>
+      </c>
+      <c r="X48" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="12.7" customHeight="1" s="22">
+      <c r="A49" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Chandurthi_</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>409</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S49" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" s="12" t="n">
+        <v>836</v>
+      </c>
+      <c r="U49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="12" t="n">
+        <v>836</v>
+      </c>
+      <c r="X49" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="12.7" customHeight="1" s="22">
+      <c r="A50" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Chandurthi</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="U50" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="X50" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" ht="12.7" customHeight="1" s="22">
+      <c r="A51" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="U51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="X51" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="12.7" customHeight="1" s="22">
+      <c r="A52" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Timmapur (P.N.)</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>255</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>249</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P52" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q52" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" s="12" t="n">
+        <v>580</v>
+      </c>
+      <c r="U52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="12" t="n">
+        <v>580</v>
+      </c>
+      <c r="X52" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" ht="12.7" customHeight="1" s="22">
+      <c r="A53" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S53" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" s="12" t="n">
+        <v>404</v>
+      </c>
+      <c r="U53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="12" t="n">
+        <v>404</v>
+      </c>
+      <c r="X53" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="12.7" customHeight="1" s="22">
+      <c r="A54" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Marrigadda</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>182</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="11" t="n">
+        <v>159</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S54" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T54" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="U54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="X54" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="12.7" customHeight="1" s="22">
+      <c r="A55" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Marrigadda</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>93</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="12" t="n">
+        <v>534</v>
+      </c>
+      <c r="U55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="12" t="n">
+        <v>534</v>
+      </c>
+      <c r="X55" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="12.7" customHeight="1" s="22">
+      <c r="A56" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Jogapur</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N56" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="U56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="12" t="n">
+        <v>310</v>
+      </c>
+      <c r="X56" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="12.7" customHeight="1" s="22">
+      <c r="A57" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P57" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T57" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="U57" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="X57" s="12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" ht="12.7" customHeight="1" s="22">
+      <c r="A58" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>ee</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>264</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="O58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="12" t="n">
+        <v>487</v>
+      </c>
+      <c r="U58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="12" t="n">
+        <v>487</v>
+      </c>
+      <c r="X58" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="12.7" customHeight="1" s="22">
+      <c r="A59" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>— og « ee</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>196</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="O59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="12" t="n">
+        <v>415</v>
+      </c>
+      <c r="U59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="12" t="n">
+        <v>415</v>
+      </c>
+      <c r="X59" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="12.7" customHeight="1" s="22">
+      <c r="A60" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>“i</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="U60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="X60" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="12.7" customHeight="1" s="22">
+      <c r="A61" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 112</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>248</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="12" t="n">
+        <v>281</v>
+      </c>
+      <c r="U61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W61" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="X61" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="12.7" customHeight="1" s="22">
+      <c r="A62" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 113</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>356</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>264</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R62" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S62" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T62" s="12" t="n">
+        <v>761</v>
+      </c>
+      <c r="U62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W62" s="12" t="n">
+        <v>763</v>
+      </c>
+      <c r="X62" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="12.7" customHeight="1" s="22">
+      <c r="A63" s="9" t="n">
+        <v>133</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Venkatampalli</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="U63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="X63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="12.7" customHeight="1" s="22">
+      <c r="A64" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Nookalamarri |</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H64" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L64" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P64" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q64" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R64" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="U64" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="12" t="n">
+        <v>214</v>
+      </c>
+      <c r="X64" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="12.7" customHeight="1" s="22">
+      <c r="A65" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 136</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="11" t="n">
+        <v>263</v>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N65" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O65" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R65" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S65" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="U65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="X65" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="12.7" customHeight="1" s="22">
+      <c r="A66" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Vattemula</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>333</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" s="12" t="n">
+        <v>392</v>
+      </c>
+      <c r="U66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="X66" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="12.7" customHeight="1" s="22">
+      <c r="A67" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Shatrajupalli</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="11" t="n">
+        <v>320</v>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" s="12" t="n">
+        <v>361</v>
+      </c>
+      <c r="U67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="12" t="n">
+        <v>361</v>
+      </c>
+      <c r="X67" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="12.7" customHeight="1" s="22">
+      <c r="A68" s="9" t="n">
+        <v>142</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Shatraiupalle</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" s="11" t="n">
+        <v>259</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M68" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N68" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P68" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S68" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" s="12" t="n">
+        <v>609</v>
+      </c>
+      <c r="U68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" s="12" t="n">
+        <v>609</v>
+      </c>
+      <c r="X68" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="12.7" customHeight="1" s="22">
+      <c r="A69" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Shatrajupalle</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H69" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="N69" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S69" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" s="12" t="n">
+        <v>358</v>
+      </c>
+      <c r="U69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="12" t="n">
+        <v>358</v>
+      </c>
+      <c r="X69" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="12.7" customHeight="1" s="22">
+      <c r="A70" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Chekkapalli.</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>268</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>178</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="11" t="n">
+        <v>428</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="N70" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S70" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T70" s="12" t="n">
+        <v>949</v>
+      </c>
+      <c r="U70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="12" t="n">
+        <v>949</v>
+      </c>
+      <c r="X70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="12.7" customHeight="1" s="22">
+      <c r="A71" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Edurugatta</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="H71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="U71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="X71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="12.7" customHeight="1" s="22">
+      <c r="A72" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>IPasunoor.</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P72" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="S72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="12" t="n">
+        <v>358</v>
+      </c>
+      <c r="U72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="12" t="n">
+        <v>358</v>
+      </c>
+      <c r="X72" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="12.7" customHeight="1" s="22">
+      <c r="A73" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="12.7" customHeight="1" s="22">
+      <c r="A74" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="11" t="n">
+        <v>294</v>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N74" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q74" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R74" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S74" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T74" s="12" t="n">
+        <v>404</v>
+      </c>
+      <c r="U74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="12" t="n">
+        <v>404</v>
+      </c>
+      <c r="X74" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="12.7" customHeight="1" s="22">
+      <c r="A75" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P75" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q75" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R75" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S75" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="U75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="X75" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="12.7" customHeight="1" s="22">
+      <c r="A76" s="9" t="n">
+        <v>152</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>'Vemulawada</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>259</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>198</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N76" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S76" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T76" s="12" t="n">
+        <v>733</v>
+      </c>
+      <c r="U76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="12" t="n">
+        <v>733</v>
+      </c>
+      <c r="X76" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="12.7" customHeight="1" s="22">
+      <c r="A77" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>163</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="11" t="n">
+        <v>374</v>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T77" s="12" t="n">
+        <v>576</v>
+      </c>
+      <c r="U77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="12" t="n">
+        <v>576</v>
+      </c>
+      <c r="X77" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="12.7" customHeight="1" s="22">
+      <c r="A78" s="9" t="n">
+        <v>154</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T78" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="U78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="X78" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="12.7" customHeight="1" s="22">
+      <c r="A79" s="9" t="n">
+        <v>163</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T79" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="U79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="X79" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" ht="12.7" customHeight="1" s="22">
+      <c r="A80" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>378</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T80" s="12" t="n">
+        <v>412</v>
+      </c>
+      <c r="U80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="12" t="n">
+        <v>412</v>
+      </c>
+      <c r="X80" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="12.7" customHeight="1" s="22">
+      <c r="A81" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="11" t="n">
+        <v>254</v>
+      </c>
+      <c r="H81" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="12" t="n">
+        <v>403</v>
+      </c>
+      <c r="U81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="12" t="n">
+        <v>403</v>
+      </c>
+      <c r="X81" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="12.7" customHeight="1" s="22">
+      <c r="A82" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Soy recee! ©)</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="U82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="X82" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="12.7" customHeight="1" s="22">
+      <c r="A83" s="9" t="n">
+        <v>168</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Be acl</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U83" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="X83" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" ht="12.7" customHeight="1" s="22">
+      <c r="A84" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>IChinthakunta</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" s="11" t="n">
+        <v>257</v>
+      </c>
+      <c r="H84" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>446</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="12.7" customHeight="1" s="22">
+      <c r="A85" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>layavaram</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="U85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="X85" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="12.7" customHeight="1" s="22">
+      <c r="A86" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>lTandrival</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G86" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="H86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="U86" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="12" t="n">
+        <v>584</v>
+      </c>
+      <c r="X86" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="12.7" customHeight="1" s="22">
+      <c r="A87" s="9" t="n">
+        <v>173</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>loambheer puur</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="11" t="n">
+        <v>1186</v>
+      </c>
+      <c r="H87" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="12" t="n">
+        <v>1210</v>
+      </c>
+      <c r="U87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="12" t="n">
+        <v>1210</v>
+      </c>
+      <c r="X87" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="12.7" customHeight="1" s="22">
+      <c r="A88" s="9" t="n">
+        <v>174</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>laa _thepr fixie</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M88" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="U88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="X88" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="12.7" customHeight="1" s="22">
+      <c r="A89" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 175</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="12.7" customHeight="1" s="22">
+      <c r="A90" s="9" t="n">
+        <v>176</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>rotaram |</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="U90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" ht="12.7" customHeight="1" s="22">
+      <c r="A91" s="9" t="n">
+        <v>177</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Nalikota</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L91" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O91" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P91" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R91" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S91" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T91" s="12" t="n">
+        <v>357</v>
+      </c>
+      <c r="U91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="12" t="n">
+        <v>357</v>
+      </c>
+      <c r="X91" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="12.7" customHeight="1" s="22">
+      <c r="A92" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Nampualli_</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>347</v>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G92" s="11" t="n">
+        <v>246</v>
+      </c>
+      <c r="H92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L92" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q92" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R92" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S92" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T92" s="12" t="n">
+        <v>651</v>
+      </c>
+      <c r="U92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="12" t="n">
+        <v>651</v>
+      </c>
+      <c r="X92" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="12.7" customHeight="1" s="22">
+      <c r="A93" s="9" t="n">
+        <v>179</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Kodumunia</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="H93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="M93" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O93" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P93" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T93" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="U93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="X93" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" ht="12.7" customHeight="1" s="22">
+      <c r="A94" s="9" t="n">
+        <v>181</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Anupuram</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H94" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="U94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="X94" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" ht="12.7" customHeight="1" s="22">
+      <c r="A95" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Sankepalli _</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P95" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S95" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="U95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="X95" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" ht="12.7" customHeight="1" s="22">
+      <c r="A96" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Sankepalli</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P96" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R96" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="U96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="X96" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" ht="12.7" customHeight="1" s="22">
+      <c r="A97" s="9" t="n">
+        <v>186</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>ey orcealllH/</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S97" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="U97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" ht="12.7" customHeight="1" s="22">
+      <c r="A98" s="9" t="n">
+        <v>187</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Marrimadla</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G98" s="11" t="n">
+        <v>1169</v>
+      </c>
+      <c r="H98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="M98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R98" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="12" t="n">
+        <v>1227</v>
+      </c>
+      <c r="U98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>1227</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" ht="12.7" customHeight="1" s="22">
+      <c r="A99" s="9" t="n">
+        <v>188</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Marrimadla</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>1159</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H99" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L99" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="S99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>1348</v>
+      </c>
+      <c r="U99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>1348</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" ht="12.7" customHeight="1" s="22">
+      <c r="A100" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Vattimalla</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>133</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>159</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G100" s="11" t="n">
+        <v>169</v>
+      </c>
+      <c r="H100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K100" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S100" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="T100" s="12" t="n">
+        <v>512</v>
+      </c>
+      <c r="U100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="12" t="n">
+        <v>512</v>
+      </c>
+      <c r="X100" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="12.7" customHeight="1" s="22">
+      <c r="A101" s="9" t="n">
+        <v>190</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>i ti“ i</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N101" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="U101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="12.7" customHeight="1" s="22">
+      <c r="A102" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Vattimalla</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M102" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="N102" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="U102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="X102" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="12.7" customHeight="1" s="22">
+      <c r="A103" s="9" t="n">
+        <v>192</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Nimmapalli.</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" s="11" t="n">
+        <v>207</v>
+      </c>
+      <c r="H103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P103" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R103" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="U103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="X103" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" ht="12.7" customHeight="1" s="22">
+      <c r="A104" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Nimmapalli</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G104" s="11" t="n">
+        <v>353</v>
+      </c>
+      <c r="H104" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N104" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O104" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P104" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R104" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S104" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>406</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>425</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="12.7" customHeight="1" s="22">
+      <c r="A105" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Kondapur (PN)</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G105" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="H105" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M105" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N105" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O105" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P105" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q105" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R105" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S105" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" s="12" t="n">
+        <v>404</v>
+      </c>
+      <c r="U105" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="12" t="n">
+        <v>412</v>
+      </c>
+      <c r="X105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" ht="12.7" customHeight="1" s="22">
+      <c r="A106" s="9" t="n">
+        <v>196</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Bavusaipeta</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O106" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P106" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q106" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="R106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="U106" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="X106" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="12.7" customHeight="1" s="22">
+      <c r="A107" s="9" t="n">
+        <v>198</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Mamidipalli</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>268</v>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" s="11" t="n">
+        <v>163</v>
+      </c>
+      <c r="H107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="12" t="n">
+        <v>461</v>
+      </c>
+      <c r="U107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="12" t="n">
+        <v>461</v>
+      </c>
+      <c r="X107" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" ht="12.7" customHeight="1" s="22">
+      <c r="A108" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Venkatraopeta</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="N108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P108" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="U108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" ht="12.7" customHeight="1" s="22">
+      <c r="A109" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Konaracpeta</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="G109" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M109" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N109" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P109" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q109" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R109" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S109" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="U109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="X109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" ht="12.7" customHeight="1" s="22">
+      <c r="A110" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Konaraopeta</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>1194</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M110" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N110" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O110" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P110" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q110" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R110" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S110" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="12" t="n">
+        <v>1262</v>
+      </c>
+      <c r="U110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="12" t="n">
+        <v>1262</v>
+      </c>
+      <c r="X110" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" ht="12.7" customHeight="1" s="22">
+      <c r="A111" s="9" t="n">
+        <v>203</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Konaraopeta</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G111" s="11" t="n">
+        <v>237</v>
+      </c>
+      <c r="H111" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N111" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P111" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q111" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R111" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="U111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="X111" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" ht="12.7" customHeight="1" s="22">
+      <c r="A112" s="9" t="n">
+        <v>204</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 204</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="U112" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" ht="12.7" customHeight="1" s="22">
+      <c r="A113" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="H113" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M113" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="N113" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P113" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R113" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S113" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="12" t="n">
+        <v>283</v>
+      </c>
+      <c r="U113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>283</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" ht="12.7" customHeight="1" s="22">
+      <c r="A114" s="9" t="n">
+        <v>237</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Kacharam</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="U114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W114" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="X114" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" ht="12.7" customHeight="1" s="22">
+      <c r="A115" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Martanapeta.</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="11" t="n">
+        <v>288</v>
+      </c>
+      <c r="H115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M115" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" s="12" t="n">
+        <v>439</v>
+      </c>
+      <c r="U115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="12" t="n">
+        <v>439</v>
+      </c>
+      <c r="X115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" ht="12.7" customHeight="1" s="22">
+      <c r="A116" s="9" t="n">
+        <v>312</v>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>ISuddala.</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>158</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G116" s="11" t="n">
+        <v>207</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M116" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="N116" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P116" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S116" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" s="12" t="n">
+        <v>533</v>
+      </c>
+      <c r="U116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="12" t="n">
+        <v>533</v>
+      </c>
+      <c r="X116" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" ht="12.7" customHeight="1" s="22">
+      <c r="A117" s="9" t="n">
+        <v>313</v>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Polling Station 313</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P117" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="U117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" ht="12.7" customHeight="1" s="22">
+      <c r="A118" s="9" t="n">
+        <v>710</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>l\Kanagarthi</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K118" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O118" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R118" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S118" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="U118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="X118" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" ht="12.7" customHeight="1" s="22">
+      <c r="A119" s="9" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Vemulawada</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>1146</v>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H119" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M119" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T119" s="12" t="n">
+        <v>1303</v>
+      </c>
+      <c r="U119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="12" t="n">
+        <v>1303</v>
+      </c>
+      <c r="X119" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" ht="12.7" customHeight="1" s="22">
+      <c r="A120" s="9" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>'Vemulawada</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>367</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>159</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" s="11" t="n">
+        <v>373</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K120" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M120" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="N120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O120" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R120" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S120" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T120" s="12" t="n">
+        <v>957</v>
+      </c>
+      <c r="U120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="12" t="n">
+        <v>957</v>
+      </c>
+      <c r="X120" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" ht="12.7" customHeight="1" s="22">
+      <c r="A121" s="9" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>iVemulawada</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" s="11" t="n">
+        <v>198</v>
+      </c>
+      <c r="H121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S121" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" s="12" t="n">
+        <v>335</v>
+      </c>
+      <c r="U121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="12" t="n">
+        <v>335</v>
+      </c>
+      <c r="X121" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" ht="12.7" customHeight="1" s="22">
+      <c r="A122" s="9" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>lVemulawada</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>254</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G122" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H122" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N122" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P122" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T122" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="U122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="X122" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" ht="12.7" customHeight="1" s="22">
+      <c r="A123" s="9" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>INacaram elt</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>429</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="H123" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="N123" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O123" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R123" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S123" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T123" s="12" t="n">
+        <v>653</v>
+      </c>
+      <c r="U123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="12" t="n">
+        <v>653</v>
+      </c>
+      <c r="X123" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" ht="12.7" customHeight="1" s="22">
+      <c r="A124" s="9" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>|Malkapeta.</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M124" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="N124" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P124" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q124" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R124" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S124" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T124" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="U124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="X124" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" ht="12.7" customHeight="1" s="22">
+      <c r="A125" s="9" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>|Malkapeta</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>129</v>
+      </c>
+      <c r="G125" s="11" t="n">
+        <v>1182</v>
+      </c>
+      <c r="H125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P125" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q125" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="R125" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" s="12" t="n">
+        <v>1371</v>
+      </c>
+      <c r="U125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W125" s="12" t="n">
+        <v>1381</v>
+      </c>
+      <c r="X125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" ht="13.65" customHeight="1" s="22">
+      <c r="A126" s="13" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="15" t="n">
-        <v>188</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>167</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>263</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <v>854</v>
-      </c>
-      <c r="K21" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="L21" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="M21" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="N21" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="P21" s="15" t="n">
-        <v>1557</v>
-      </c>
-      <c r="Q21" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="R21" s="15" t="n">
-        <v>47</v>
-      </c>
-      <c r="S21" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="T21" s="15" t="n">
-        <v>4596</v>
-      </c>
-      <c r="U21" s="15" t="n">
-        <v>266</v>
-      </c>
-      <c r="V21" s="15" t="n">
-        <v>267</v>
-      </c>
-      <c r="W21" s="15" t="n">
-        <v>5129</v>
-      </c>
-      <c r="X21" s="15" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" ht="13.65" customHeight="1" s="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B126" s="14" t="n"/>
+      <c r="C126" s="15" t="n">
+        <v>17625</v>
+      </c>
+      <c r="D126" s="15" t="n">
+        <v>4714</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>17650</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>246</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>1039</v>
+      </c>
+      <c r="J126" s="15" t="n">
+        <v>295</v>
+      </c>
+      <c r="K126" s="15" t="n">
+        <v>166</v>
+      </c>
+      <c r="L126" s="15" t="n">
+        <v>378</v>
+      </c>
+      <c r="M126" s="15" t="n">
+        <v>1375</v>
+      </c>
+      <c r="N126" s="15" t="n">
+        <v>298</v>
+      </c>
+      <c r="O126" s="15" t="n">
+        <v>455</v>
+      </c>
+      <c r="P126" s="15" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q126" s="15" t="n">
+        <v>261</v>
+      </c>
+      <c r="R126" s="15" t="n">
+        <v>363</v>
+      </c>
+      <c r="S126" s="15" t="n">
+        <v>362</v>
+      </c>
+      <c r="T126" s="15" t="n">
+        <v>48810</v>
+      </c>
+      <c r="U126" s="15" t="n">
+        <v>192</v>
+      </c>
+      <c r="V126" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="W126" s="15" t="n">
+        <v>49035</v>
+      </c>
+      <c r="X126" s="15" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" ht="13.65" customHeight="1" s="22">
+      <c r="A127" s="16" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="13.65" customHeight="1" s="22">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B127" s="17" t="n"/>
+      <c r="C127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" ht="13.65" customHeight="1" s="22">
+      <c r="A128" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="20" t="n">
-        <v>188</v>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>167</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="I23" s="20" t="n">
-        <v>263</v>
-      </c>
-      <c r="J23" s="20" t="n">
-        <v>854</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="L23" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="N23" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="P23" s="20" t="n">
-        <v>1557</v>
-      </c>
-      <c r="Q23" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="R23" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="S23" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="T23" s="20" t="n">
-        <v>4596</v>
-      </c>
-      <c r="U23" s="20" t="n">
-        <v>266</v>
-      </c>
-      <c r="V23" s="20" t="n">
-        <v>267</v>
-      </c>
-      <c r="W23" s="20" t="n">
-        <v>5129</v>
-      </c>
-      <c r="X23" s="21" t="n">
-        <v>86</v>
+      <c r="B128" s="19" t="n"/>
+      <c r="C128" s="20" t="n">
+        <v>17625</v>
+      </c>
+      <c r="D128" s="20" t="n">
+        <v>4714</v>
+      </c>
+      <c r="E128" s="20" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F128" s="20" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G128" s="20" t="n">
+        <v>17650</v>
+      </c>
+      <c r="H128" s="20" t="n">
+        <v>246</v>
+      </c>
+      <c r="I128" s="20" t="n">
+        <v>1039</v>
+      </c>
+      <c r="J128" s="20" t="n">
+        <v>295</v>
+      </c>
+      <c r="K128" s="20" t="n">
+        <v>166</v>
+      </c>
+      <c r="L128" s="20" t="n">
+        <v>378</v>
+      </c>
+      <c r="M128" s="20" t="n">
+        <v>1375</v>
+      </c>
+      <c r="N128" s="20" t="n">
+        <v>298</v>
+      </c>
+      <c r="O128" s="20" t="n">
+        <v>455</v>
+      </c>
+      <c r="P128" s="20" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q128" s="20" t="n">
+        <v>261</v>
+      </c>
+      <c r="R128" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="S128" s="20" t="n">
+        <v>362</v>
+      </c>
+      <c r="T128" s="20" t="n">
+        <v>48810</v>
+      </c>
+      <c r="U128" s="20" t="n">
+        <v>192</v>
+      </c>
+      <c r="V128" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="W128" s="20" t="n">
+        <v>49035</v>
+      </c>
+      <c r="X128" s="21" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
